--- a/figure4/figure4B-C.Each_type_stimulation/plotting/data/Labellar_candidate_stimulation.xlsx
+++ b/figure4/figure4B-C.Each_type_stimulation/plotting/data/Labellar_candidate_stimulation.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>0Hz</t>
@@ -488,161 +493,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>high_salt</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.105</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>3.505</v>
+        <v>3.27</v>
       </c>
       <c r="E2" t="n">
-        <v>4.335</v>
+        <v>10.405</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7</v>
+        <v>17.72</v>
       </c>
       <c r="G2" t="n">
-        <v>6.145</v>
+        <v>23.96</v>
       </c>
       <c r="H2" t="n">
-        <v>7.81</v>
+        <v>29.16</v>
       </c>
       <c r="I2" t="n">
-        <v>8.960000000000001</v>
+        <v>33.36</v>
       </c>
       <c r="J2" t="n">
-        <v>10.44</v>
+        <v>37.24</v>
       </c>
       <c r="K2" t="n">
-        <v>11.39</v>
+        <v>41.295</v>
       </c>
       <c r="L2" t="n">
-        <v>12.865</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="D3" t="n">
-        <v>3.27</v>
+        <v>12.69</v>
       </c>
       <c r="E3" t="n">
-        <v>10.405</v>
+        <v>25.185</v>
       </c>
       <c r="F3" t="n">
-        <v>17.72</v>
+        <v>35.065</v>
       </c>
       <c r="G3" t="n">
-        <v>23.96</v>
+        <v>42.02</v>
       </c>
       <c r="H3" t="n">
-        <v>29.16</v>
+        <v>47.885</v>
       </c>
       <c r="I3" t="n">
-        <v>33.36</v>
+        <v>54.235</v>
       </c>
       <c r="J3" t="n">
-        <v>37.24</v>
+        <v>59.04</v>
       </c>
       <c r="K3" t="n">
-        <v>41.295</v>
+        <v>62.87</v>
       </c>
       <c r="L3" t="n">
-        <v>45.7</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.46</v>
+        <v>8.635</v>
       </c>
       <c r="D4" t="n">
-        <v>12.69</v>
+        <v>16.5</v>
       </c>
       <c r="E4" t="n">
-        <v>25.185</v>
+        <v>23.335</v>
       </c>
       <c r="F4" t="n">
-        <v>35.065</v>
+        <v>29.27</v>
       </c>
       <c r="G4" t="n">
-        <v>42.02</v>
+        <v>32.29</v>
       </c>
       <c r="H4" t="n">
-        <v>47.885</v>
+        <v>36.68</v>
       </c>
       <c r="I4" t="n">
-        <v>54.235</v>
+        <v>39.22</v>
       </c>
       <c r="J4" t="n">
-        <v>59.04</v>
+        <v>41.945</v>
       </c>
       <c r="K4" t="n">
-        <v>62.87</v>
+        <v>44.01</v>
       </c>
       <c r="L4" t="n">
-        <v>65.94</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>high_salt</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8.635</v>
+        <v>0.105</v>
       </c>
       <c r="D5" t="n">
-        <v>16.5</v>
+        <v>3.505</v>
       </c>
       <c r="E5" t="n">
-        <v>23.335</v>
+        <v>4.335</v>
       </c>
       <c r="F5" t="n">
-        <v>29.27</v>
+        <v>4.7</v>
       </c>
       <c r="G5" t="n">
-        <v>32.29</v>
+        <v>6.145</v>
       </c>
       <c r="H5" t="n">
-        <v>36.68</v>
+        <v>7.81</v>
       </c>
       <c r="I5" t="n">
-        <v>39.22</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>41.945</v>
+        <v>10.44</v>
       </c>
       <c r="K5" t="n">
-        <v>44.01</v>
+        <v>11.39</v>
       </c>
       <c r="L5" t="n">
-        <v>45.44</v>
+        <v>12.865</v>
       </c>
     </row>
     <row r="6">
